--- a/public/templates/teacher_upload_template.xlsx
+++ b/public/templates/teacher_upload_template.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="Template" sheetId="1" r:id="rId1"/>
+    <sheet name="Teachers" sheetId="1" r:id="rId1"/>
   </sheets>
 </workbook>
 </file>
@@ -424,25 +424,25 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>John</v>
+        <v>Rajesh</v>
       </c>
       <c r="B2" t="str">
-        <v>Doe</v>
+        <v>Sharma</v>
       </c>
       <c r="C2" t="str">
-        <v>john.teacher@example.com</v>
+        <v>r.sharma@school.internal</v>
       </c>
       <c r="D2" t="str">
-        <v>password123</v>
+        <v>Teacher@123</v>
       </c>
       <c r="E2" t="str">
-        <v>9876543210</v>
+        <v>9876543211</v>
       </c>
       <c r="F2" t="str">
-        <v>2026-06-01</v>
+        <v>2024-06-01</v>
       </c>
       <c r="G2" t="str">
-        <v>M.Sc., B.Ed.</v>
+        <v>M.Sc, B.Ed</v>
       </c>
     </row>
   </sheetData>

--- a/public/templates/teacher_upload_template.xlsx
+++ b/public/templates/teacher_upload_template.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:H2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -421,6 +421,9 @@
       <c r="G1" t="str">
         <v>qualification</v>
       </c>
+      <c r="H1" t="str">
+        <v>subjects</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -442,12 +445,15 @@
         <v>2024-06-01</v>
       </c>
       <c r="G2" t="str">
-        <v>M.Sc, B.Ed</v>
+        <v>M.Sc B.Ed</v>
+      </c>
+      <c r="H2" t="str">
+        <v>Science</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H2"/>
   </ignoredErrors>
 </worksheet>
 </file>